--- a/dataset/cbs.xlsx
+++ b/dataset/cbs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="245">
   <si>
     <t>entry</t>
   </si>
@@ -43,31 +43,493 @@
     <t>test</t>
   </si>
   <si>
+    <t>CC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>KWOLFJPFCHCOCG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey et al., J. Am. Chem. Soc. 1987, 109, 7925-7926.</t>
+  </si>
+  <si>
+    <t>CCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>KRIOVPPHQSLHCZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCl)c1ccccc1</t>
+  </si>
+  <si>
+    <t>IMACFCSSMIZSPP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C(C)(C)C</t>
+  </si>
+  <si>
+    <t>PJGSXYOJTGTZAV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCc2ccccc21</t>
+  </si>
+  <si>
+    <t>XHLHPRDBBAGVEG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>RIFKADJTWUGDOV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCC=C1Br</t>
+  </si>
+  <si>
+    <t>KYNHSQQWQIIFTG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1ccc2cc(C(C)=O)ccc2c1</t>
+  </si>
+  <si>
+    <t>GGWCZBGAIGGTDA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)CCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>XVRCVKWYKYJEIG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)CCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>GRIWFUFDJOESIC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(=O)CCC(=O)c1ccc(OC)c(OC)c1</t>
+  </si>
+  <si>
+    <t>RUENABICCRWAEK-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COC(CC1=CCCC1=O)OC</t>
+  </si>
+  <si>
+    <t>JDVISUFZLXDPQJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey et al., Tetrahedron Lett. 1988, 29, 3201-3204.</t>
+  </si>
+  <si>
+    <t>C=CC1=C(C)C(=O)CCC1(C)C</t>
+  </si>
+  <si>
+    <t>FFZLOJDYTNKOCQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey, P. S. Jardine, J. C. Rohloff, J. Am. Chem. Soc., 1988, 110, 3672-3273.</t>
+  </si>
+  <si>
+    <t>O=C(CCCl)c1ccccc1</t>
+  </si>
+  <si>
+    <t>KTJRGPZVSKWRTJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey, G. A. Reichard, Tetrahedron Lett. 1989, 30, 5207-5210.</t>
+  </si>
+  <si>
+    <t>C=C(OC(=O)OCC)C1=C(C)C(=O)CCC1(C)C</t>
+  </si>
+  <si>
+    <t>HHZPPLBLSSEAQT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey, P. D. S. Jardine, Tetrahedron Lett. 1989, 30, 7297-7300.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cccc(Br)c1</t>
+  </si>
+  <si>
+    <t>JYAQYXOVOHJRCS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C. P. Chen et al., Tetrahedron Lett. 1991, 32, 7175-7178.</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(C)=O)c1</t>
+  </si>
+  <si>
+    <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc2ccccc2c1</t>
+  </si>
+  <si>
+    <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCC=C1Br</t>
+  </si>
+  <si>
+    <t>WJZDXONSAPNKGB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey, K. S. Rao, Tetrahedron lett. 1991, 32, 4623.</t>
+  </si>
+  <si>
+    <t>CC(=O)C(c1ccccc1)(c1ccccc1)c1ccccc1</t>
+  </si>
+  <si>
+    <t>LZIVBWLOLYCDAZ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>E. J. Corey, et al., Tetrahedron lett. 1991, 32, 6835.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cccs1</t>
+  </si>
+  <si>
+    <t>WYJOVVXUZNRJQY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>G. J. Quallich, T. M. Woodall, Tetrahedron Lett. 1993, 34, 785-788.</t>
+  </si>
+  <si>
+    <t>CN(C)CCC(=O)c1ccc(Cl)c(Cl)c1</t>
+  </si>
+  <si>
+    <t>LZXMNZWXKWSYMY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G. J. Quallich, T. M. Woodall, Tetrahedron Lett. 1993, 34, 785-788. </t>
+  </si>
+  <si>
+    <t>O=C1CCOc2ccccc21</t>
+  </si>
+  <si>
+    <t>MSTDXOZUKAQDRL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCSc2ccccc21</t>
+  </si>
+  <si>
+    <t>CVQSWZMJOGOPAV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc(C#N)cc1</t>
+  </si>
+  <si>
+    <t>NLPHXWGWBKZSJC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)CCCC#N</t>
+  </si>
+  <si>
+    <t>AEVMBQIIZGKQRB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(C)=O</t>
+  </si>
+  <si>
+    <t>QQZOPKMRPOGIEB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc(F)cc1</t>
+  </si>
+  <si>
+    <t>ZDPAWHACYDRYIW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>D. J. Mathre, et al., J. Org. Chem. 1993, 58, 2880-2888.</t>
+  </si>
+  <si>
+    <t>COc1ccc(C(C)=O)cc1</t>
+  </si>
+  <si>
+    <t>NTPLXRHDUXRPNE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCCc2ccccc21</t>
+  </si>
+  <si>
+    <t>KWHUHTFXMNQHAA-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCc2ccccc21</t>
+  </si>
+  <si>
+    <t>QNXSIUBBGPHDDE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC[C@@H](C)C[C@@H](C)C[C@@H](C)CC(C)=O</t>
+  </si>
+  <si>
+    <t>BTJCLODZUWAGCT-IJLUTSLNSA-N</t>
+  </si>
+  <si>
+    <t>M. Morr, C. Proppe, V. Wray, Liebigs Ann. 1995, 11, 2001-2004.</t>
+  </si>
+  <si>
+    <t>COc1cc(C(C)=O)ccc1OC(C)=O</t>
+  </si>
+  <si>
+    <t>GCVAEUQDYWOLCF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>V. U. Ponzo, T. S. Kaufman, Tetrahedron Lett. 1995, 36, 9105-9108.</t>
+  </si>
+  <si>
+    <t>O=C1CCCC1(c1ccccc1)c1ccccc1</t>
+  </si>
+  <si>
+    <t>CBOPQVXWIKRPKD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>S. E. Denmark, et al., J. Org. Chem. 1995, 60, 3205-3220.</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(C)=O)c1OC</t>
+  </si>
+  <si>
+    <t>FODUVZQSLRHUMC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>T. S. Kaufman, Tetrahedron Lett. 1996, 37, 5329-5332.</t>
+  </si>
+  <si>
+    <t>COc1ccccc1C(C)=O</t>
+  </si>
+  <si>
+    <t>DWPLEOPKBWNPQV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccccc1Oc1ccccc1</t>
+  </si>
+  <si>
+    <t>KPBCVVSDGJBODL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(C)=O)c1Oc1ccccc1</t>
+  </si>
+  <si>
+    <t>CLEOFCSYMMMFEG-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>COc1c(C)c2c(c([Si](C)(C)C(C)(C)C)c1CC(=O)C1=CCCC1)C(=O)OC2</t>
+  </si>
+  <si>
+    <t>QNEZGBYRBDJSFT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>D. B. Smith, et al., J. Org. Chem. 1996, 61, 2236.</t>
+  </si>
+  <si>
+    <t>CC(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>UPEUQDJSUFHFQP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>K. A. Parker, M. W. Ledeboer, J. Org. Chem. 1996, 61, 3214-3217.</t>
+  </si>
+  <si>
+    <t>CCC(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>XAJIQJSLJKBJTP-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>BXYHYUVKQUDMJD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)C(=O)C#Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>AOOHPXMHKBITKB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(C#Cc1ccccc1)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>PFIKCDNZZJYSMK-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(=O)CCCCCCC</t>
+  </si>
+  <si>
+    <t>UWEKKSOZSXKQOQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>C#CC(=O)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>VRZSUVFVIIVLPV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCC/C1=C/c1ccccc1</t>
+  </si>
+  <si>
+    <t>ZFJFROHCPHULKY-LUAWRHEFSA-N</t>
+  </si>
+  <si>
+    <t>A. F. Simpson, et al., Tetrahedron Asymmetry 1997, 8, 673-676.</t>
+  </si>
+  <si>
+    <t>O=C1CCC/C1=C\c1ccccc1</t>
+  </si>
+  <si>
+    <t>ZFJFROHCPHULKY-PKNBQFBNSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCCC/C1=C\c1ccccc1</t>
+  </si>
+  <si>
+    <t>VCDPHYIZVFJQCD-ZRDIBKRKSA-N</t>
+  </si>
+  <si>
     <t>O=C1CCCC1=C1CCCC1</t>
   </si>
   <si>
     <t>NYSYNXRPXJZYFY-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>A. F. Simpson, et al., Tetrahedron Asymmetry 1997, 8, 673-676.</t>
-  </si>
-  <si>
-    <t>CCC(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>XAJIQJSLJKBJTP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>K. A. Parker, M. W. Ledeboer, J. Org. Chem. 1996, 61, 3214-3217.</t>
-  </si>
-  <si>
-    <t>O=C1CCCC=C1Br</t>
-  </si>
-  <si>
-    <t>KYNHSQQWQIIFTG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey et al., J. Am. Chem. Soc. 1987, 109, 7925-7926.</t>
+    <t>CC(C)/C=C1\CCCC1=O</t>
+  </si>
+  <si>
+    <t>GSSRLAIHCZNDAA-SOFGYWHQSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCC/C=C1\CCCC1=O</t>
+  </si>
+  <si>
+    <t>WWHQKPBWGGRGPU-FMIVXFBMSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCN2C(=O)CCC=C12</t>
+  </si>
+  <si>
+    <t>XLLDMGPEOCTHPV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1CCN2C(=O)CCCC=C12</t>
+  </si>
+  <si>
+    <t>ZMOYCFVCHCPLPQ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)OC(=O)CN1CCC2(CC1)C(=O)Cc1ccccc12</t>
+  </si>
+  <si>
+    <t>IFROQBZVEYKUHT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>T. Takemoto, et al., Tetrahedron Asymmetry. 1998, 10, 1787-1793.</t>
+  </si>
+  <si>
+    <t>C=C(CC)C(C)=O</t>
+  </si>
+  <si>
+    <t>UOTSYAILGSUTAC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Takayama, Hiromitsu, et al. 1999, 1772-1773.</t>
+  </si>
+  <si>
+    <t>CC1=C(Br)C(=O)CCC1</t>
+  </si>
+  <si>
+    <t>ZIAUNOWNSIKDPU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>M. Hansson, et al., Journal of the Chemical Society, Perkin Transactions. 2002, 2, 763-767</t>
+  </si>
+  <si>
+    <t>CC(=O)C(C)C</t>
+  </si>
+  <si>
+    <t>SYBYTAAJFKOIEJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Huertas, Ramón E., Joseph A. Corella, and John A. Soderquist. Tetrahedron lett. 2003, 44, 4435-4437.</t>
+  </si>
+  <si>
+    <t>COc1ccc(C(=O)CCl)cc1</t>
+  </si>
+  <si>
+    <t>MCRINSAETDOKDE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>S. Degni, C. E. Wilen, A. Rosling, Tetrahedron Asymmetry. 2004, 15, 1495-1499.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccc(C)cc1</t>
+  </si>
+  <si>
+    <t>GNKZMNRKLCTJAY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC1=CCCCC1=O</t>
+  </si>
+  <si>
+    <t>LKTNAAYQZJAXCJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>D. Bourgeois, et al., Tetrahedron. 2006. 62. 483-495.</t>
+  </si>
+  <si>
+    <t>Cc1ccc(S(=O)(=O)NCc2ccccc2C(=O)c2ccccc2)cc1</t>
+  </si>
+  <si>
+    <t>AJJMCZDTONCKDU-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Cho, Byung Tae. Tetrahedron, 2006, 62. 7621-7643.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1csc2ccccc12</t>
+  </si>
+  <si>
+    <t>ZTTZKDDWXHQKSY-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Y. Yokoyama, et al. Angew. Chem. Int. Ed. 2009, 48, 4521-4523.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1cc2ccccc2s1</t>
+  </si>
+  <si>
+    <t>SGSGCQGCVKWRNM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(=O)Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>QCCDLTOVEPVEJK-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>T. Ema, et al., Tetrahedron 2009, 65, 9583-9591.</t>
+  </si>
+  <si>
+    <t>CC(=O)CCc1ccccc1</t>
+  </si>
+  <si>
+    <t>AKGGYBADQZYZPD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(=O)Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>DYQAZJQDLPPHNB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCc1ccccc1)Cc1ccccc1</t>
+  </si>
+  <si>
+    <t>PFJFIFJKDPIALO-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(Cc1ccccc1)C1CCCCC1</t>
@@ -76,64 +538,34 @@
     <t>NHBBLULITNXPDY-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>T. Ema, et al., Tetrahedron 2009, 65, 9583-9591.</t>
-  </si>
-  <si>
-    <t>O=C1CCc2ccccc21</t>
-  </si>
-  <si>
-    <t>QNXSIUBBGPHDDE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>D. J. Mathre, et al., J. Org. Chem. 1993, 58, 2880-2888.</t>
-  </si>
-  <si>
-    <t>COc1c(C)c2c(c([Si](C)(C)C(C)(C)C)c1CC(=O)C1=CCCC1)C(=O)OC2</t>
-  </si>
-  <si>
-    <t>QNEZGBYRBDJSFT-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>D. B. Smith, et al., J. Org. Chem. 1996, 61, 2236.</t>
-  </si>
-  <si>
-    <t>CC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>RIFKADJTWUGDOV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCc1ccccc1)Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>PFJFIFJKDPIALO-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC1=CCCCC1=O</t>
-  </si>
-  <si>
-    <t>LKTNAAYQZJAXCJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>D. Bourgeois, et al., Tetrahedron. 2006. 62. 483-495.</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc2ccccc2c1</t>
-  </si>
-  <si>
-    <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>C. P. Chen et al., Tetrahedron Lett. 1991, 32, 7175-7178.</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccs1</t>
-  </si>
-  <si>
-    <t>WYJOVVXUZNRJQY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>G. J. Quallich, T. M. Woodall, Tetrahedron Lett. 1993, 34, 785-788.</t>
+    <t>O=C(Cc1ccccc1)c1ccccc1</t>
+  </si>
+  <si>
+    <t>OTKCEEWUXHVZQI-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(=O)CCc1ccccc1</t>
+  </si>
+  <si>
+    <t>ZGTHHNNORWULAE-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(=O)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>ICADMAXOJLUEEB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>XKGLSKVNOSHTAD-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(CCc1ccccc1)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>LFBKBXCVHMMYSM-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>O=C(CCc1ccccc1)c1ccccc1</t>
@@ -142,91 +574,88 @@
     <t>QGGZBXOADPVUPN-UHFFFAOYSA-N</t>
   </si>
   <si>
+    <t>O=C(c1ccccc1)C1CCCCC1</t>
+  </si>
+  <si>
+    <t>BMFYCFSWWDXEPB-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C1C=CCC1</t>
+  </si>
+  <si>
+    <t>BZKFMUIJRXWWQK-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O. Hamed, et al., Tetrahedron Lett. 2010, 51, 3514-3517.</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>QQXJNLYVPPBERR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>T. Yıldız, A. Yusufoğlu., Tetrahedron Asymmetry. 2010, 21, 2981-2987.</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>LHJBFOGCFZHBAJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>DJNJZIFFCJTUDS-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>ZZNDQCACFUJAKJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>LXUIUVLDNRQBQJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCCCCCCC(=O)c1ccccc1</t>
+  </si>
+  <si>
+    <t>VUXIOSYYRVXOOT-UHFFFAOYSA-N</t>
+  </si>
+  <si>
     <t>CCCCCCCCCCCCCCCCCC(=O)c1ccccc1</t>
   </si>
   <si>
     <t>DBLXXVQTWJFJFI-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>T. Yıldız, A. Yusufoğlu., Tetrahedron Asymmetry. 2010, 21, 2981-2987.</t>
-  </si>
-  <si>
-    <t>CC(=O)C(c1ccccc1)(c1ccccc1)c1ccccc1</t>
-  </si>
-  <si>
-    <t>LZIVBWLOLYCDAZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey, et al., Tetrahedron lett. 1991, 32, 6835.</t>
-  </si>
-  <si>
-    <t>C#CC(=O)CCCCCCC</t>
-  </si>
-  <si>
-    <t>UWEKKSOZSXKQOQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COC(=O)CCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>XVRCVKWYKYJEIG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc2cc(C(C)=O)ccc2c1</t>
-  </si>
-  <si>
-    <t>GGWCZBGAIGGTDA-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)C(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>AOOHPXMHKBITKB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>C=CC1=C(C)C(=O)CCC1(C)C</t>
-  </si>
-  <si>
-    <t>FFZLOJDYTNKOCQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey, P. S. Jardine, J. C. Rohloff, J. Am. Chem. Soc., 1988, 110, 3672-3273.</t>
-  </si>
-  <si>
-    <t>CC(=O)CCc1ccccc1</t>
-  </si>
-  <si>
-    <t>AKGGYBADQZYZPD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCSc2ccccc21</t>
-  </si>
-  <si>
-    <t>CVQSWZMJOGOPAV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G. J. Quallich, T. M. Woodall, Tetrahedron Lett. 1993, 34, 785-788. </t>
-  </si>
-  <si>
-    <t>CCCCC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>ICADMAXOJLUEEB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>QCCDLTOVEPVEJK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCCl)c1ccccc1</t>
-  </si>
-  <si>
-    <t>KTJRGPZVSKWRTJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey, G. A. Reichard, Tetrahedron Lett. 1989, 30, 5207-5210.</t>
+    <t>CCCCCCCCCCC(=O)c1ccc(C)cc1</t>
+  </si>
+  <si>
+    <t>ZAVHZGXNVXPEQL-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCC(=O)c1ccc(Br)cc1</t>
+  </si>
+  <si>
+    <t>UPXYDTHCXGAAOR-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCC(=O)c1ccc(O)cc1</t>
+  </si>
+  <si>
+    <t>LQWPEACAJAMZQF-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCCCCC(=O)C1CC=CCO1</t>
+  </si>
+  <si>
+    <t>VYEAAEOKYGNCAW-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>CCCCCCCCCCCCCC(=O)c1ccco1</t>
@@ -235,67 +664,64 @@
     <t>OXNUVECEMGENBT-UHFFFAOYSA-N</t>
   </si>
   <si>
-    <t>CCCCC(C)=O</t>
-  </si>
-  <si>
-    <t>QQZOPKMRPOGIEB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC(=O)CCc1ccccc1</t>
-  </si>
-  <si>
-    <t>ZGTHHNNORWULAE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCC=C1Br</t>
-  </si>
-  <si>
-    <t>WJZDXONSAPNKGB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey, K. S. Rao, Tetrahedron lett. 1991, 32, 4623.</t>
-  </si>
-  <si>
-    <t>COc1cc(C(C)=O)ccc1OC(C)=O</t>
-  </si>
-  <si>
-    <t>GCVAEUQDYWOLCF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>V. U. Ponzo, T. S. Kaufman, Tetrahedron Lett. 1995, 36, 9105-9108.</t>
-  </si>
-  <si>
-    <t>COc1ccccc1C(C)=O</t>
-  </si>
-  <si>
-    <t>DWPLEOPKBWNPQV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>T. S. Kaufman, Tetrahedron Lett. 1996, 37, 5329-5332.</t>
-  </si>
-  <si>
-    <t>COc1cccc(C(C)=O)c1</t>
-  </si>
-  <si>
-    <t>BAYUSCHCCGXLAY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>VUXIOSYYRVXOOT-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>LHJBFOGCFZHBAJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCCc2ccccc21</t>
-  </si>
-  <si>
-    <t>KWHUHTFXMNQHAA-UHFFFAOYSA-N</t>
+    <t>CCCCCCCCCCCCCC(=O)c1cccs1</t>
+  </si>
+  <si>
+    <t>PKZFXANDBXVDRM-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCC(=O)c1ccc2ccccc2c1</t>
+  </si>
+  <si>
+    <t>GRKKWJQOJDWEEN-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>CC(C)(C)c1ccc(C(=O)c2ccccc2)cc1</t>
+  </si>
+  <si>
+    <t>DFYJCXSOGSYMAJ-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>O=C(c1ccccc1)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>KZJRKRQSDZGHEC-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>Chem. Commun., 2010, 46, 8624-8626.</t>
+  </si>
+  <si>
+    <t>C=C(CCCC)C(=O)C#C[Si](C)(C)C</t>
+  </si>
+  <si>
+    <t>BVPKHWLMDSKODW-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>N. A. Morra, B. L. Pagenkopf. Org. lett. 2011, 13, 572-575.</t>
+  </si>
+  <si>
+    <t>CC(=O)c1ccccc1C</t>
+  </si>
+  <si>
+    <t>YXWWHNCQZBVZPV-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>J. H. Hutchinson, et al., "Polycyclic antagonists of lysophosphatidic acid receptors.", U.S. Patent No. 8,058,300. 15 Nov. 2011.</t>
+  </si>
+  <si>
+    <t>CC(C)(C)[Si](C)(C)Oc1ccccc1C(=O)C#C[Si](C)(C)C</t>
+  </si>
+  <si>
+    <t>OVXHPUNWJSQAEN-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t>J. Org. Chem. 2015, 80, 8, 4189–4200</t>
+  </si>
+  <si>
+    <t>COc1cccc(C(=O)C#C[Si](C)(C)C)c1O[Si](C)(C)C(C)(C)C</t>
+  </si>
+  <si>
+    <t>SZZNLQONRHATKI-UHFFFAOYSA-N</t>
   </si>
   <si>
     <t>Cc1ccc(C)c(C(=O)c2ccccc2)c1</t>
@@ -307,91 +733,13 @@
     <t>Keddie, Neil S., et al. Beilstein Journal of Organic Chemistry, 2018, 14, 106-113.</t>
   </si>
   <si>
-    <t>Cc1ccc(S(=O)(=O)NCc2ccccc2C(=O)c2ccccc2)cc1</t>
-  </si>
-  <si>
-    <t>AJJMCZDTONCKDU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cho, Byung Tae. Tetrahedron, 2006, 62. 7621-7643.</t>
-  </si>
-  <si>
-    <t>COc1cccc(C(C)=O)c1OC</t>
-  </si>
-  <si>
-    <t>FODUVZQSLRHUMC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCC/C1=C/c1ccccc1</t>
-  </si>
-  <si>
-    <t>ZFJFROHCPHULKY-LUAWRHEFSA-N</t>
-  </si>
-  <si>
-    <t>O=C(C#Cc1ccccc1)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>PFIKCDNZZJYSMK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCN2C(=O)CCC=C12</t>
-  </si>
-  <si>
-    <t>XLLDMGPEOCTHPV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCC(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>BXYHYUVKQUDMJD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCC1(c1ccccc1)c1ccccc1</t>
-  </si>
-  <si>
-    <t>CBOPQVXWIKRPKD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>S. E. Denmark, et al., J. Org. Chem. 1995, 60, 3205-3220.</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(C#N)cc1</t>
-  </si>
-  <si>
-    <t>NLPHXWGWBKZSJC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCCCC(=O)C1CC=CCO1</t>
-  </si>
-  <si>
-    <t>VYEAAEOKYGNCAW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C(C)(C)C</t>
-  </si>
-  <si>
-    <t>PJGSXYOJTGTZAV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)/C=C1\CCCC1=O</t>
-  </si>
-  <si>
-    <t>GSSRLAIHCZNDAA-SOFGYWHQSA-N</t>
-  </si>
-  <si>
-    <t>COC(=O)CCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>GRIWFUFDJOESIC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC[C@@H](C)C[C@@H](C)C[C@@H](C)CC(C)=O</t>
-  </si>
-  <si>
-    <t>BTJCLODZUWAGCT-IJLUTSLNSA-N</t>
-  </si>
-  <si>
-    <t>M. Morr, C. Proppe, V. Wray, Liebigs Ann. 1995, 11, 2001-2004.</t>
+    <t>Cc1ccc(S(=O)(=O)NCCc2ccc(C)cc2C(=O)c2ccccc2)cc1</t>
+  </si>
+  <si>
+    <t>PVSHPLKPKFIRHX-UHFFFAOYSA-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhou, Bo, et al. Nature Communications, 2019, 10., 3234. </t>
   </si>
   <si>
     <t>Cc1ccccc1C(=O)c1ccccc1</t>
@@ -401,318 +749,6 @@
   </si>
   <si>
     <t xml:space="preserve">J. Regier,et al., European Journal of Organic Chemistry ,2019, 13, 2390-2396. </t>
-  </si>
-  <si>
-    <t>O=C(Cc1ccccc1)c1ccccc1</t>
-  </si>
-  <si>
-    <t>OTKCEEWUXHVZQI-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C(C)C</t>
-  </si>
-  <si>
-    <t>SYBYTAAJFKOIEJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Huertas, Ramón E., Joseph A. Corella, and John A. Soderquist. Tetrahedron lett. 2003, 44, 4435-4437.</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>ZZNDQCACFUJAKJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)(C)c1ccc(C(=O)c2ccccc2)cc1</t>
-  </si>
-  <si>
-    <t>DFYJCXSOGSYMAJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCOc2ccccc21</t>
-  </si>
-  <si>
-    <t>MSTDXOZUKAQDRL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCC(=O)c1ccc(Br)cc1</t>
-  </si>
-  <si>
-    <t>UPXYDTHCXGAAOR-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>KRIOVPPHQSLHCZ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCc2ccccc21</t>
-  </si>
-  <si>
-    <t>XHLHPRDBBAGVEG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCN2C(=O)CCCC=C12</t>
-  </si>
-  <si>
-    <t>ZMOYCFVCHCPLPQ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)C#Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>UPEUQDJSUFHFQP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>C#CC(=O)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>VRZSUVFVIIVLPV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCCCC(=O)c1cccs1</t>
-  </si>
-  <si>
-    <t>PKZFXANDBXVDRM-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1cccc(C(C)=O)c1Oc1ccccc1</t>
-  </si>
-  <si>
-    <t>CLEOFCSYMMMFEG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(=O)CCl)cc1</t>
-  </si>
-  <si>
-    <t>MCRINSAETDOKDE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>S. Degni, C. E. Wilen, A. Rosling, Tetrahedron Asymmetry. 2004, 15, 1495-1499.</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCC(=O)c1ccc(O)cc1</t>
-  </si>
-  <si>
-    <t>LQWPEACAJAMZQF-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Cc1ccc(S(=O)(=O)NCCc2ccc(C)cc2C(=O)c2ccccc2)cc1</t>
-  </si>
-  <si>
-    <t>PVSHPLKPKFIRHX-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhou, Bo, et al. Nature Communications, 2019, 10., 3234. </t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(C)cc1</t>
-  </si>
-  <si>
-    <t>GNKZMNRKLCTJAY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>S. Degni, et al., Tetrahedron Asymmetry, 2004, 15, 1495-1499.</t>
-  </si>
-  <si>
-    <t>COC(=O)CCC(=O)c1ccc(OC)c(OC)c1</t>
-  </si>
-  <si>
-    <t>RUENABICCRWAEK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCC/C=C1\CCCC1=O</t>
-  </si>
-  <si>
-    <t>WWHQKPBWGGRGPU-FMIVXFBMSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>BMFYCFSWWDXEPB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCC(=O)c1ccc2ccccc2c1</t>
-  </si>
-  <si>
-    <t>GRKKWJQOJDWEEN-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCl)c1ccccc1</t>
-  </si>
-  <si>
-    <t>IMACFCSSMIZSPP-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>XKGLSKVNOSHTAD-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC1=C(Br)C(=O)CCC1</t>
-  </si>
-  <si>
-    <t>ZIAUNOWNSIKDPU-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>M. Hansson, et al., Journal of the Chemical Society, Perkin Transactions. 2002, 2, 763-767</t>
-  </si>
-  <si>
-    <t>O=C1CCC/C1=C\c1ccccc1</t>
-  </si>
-  <si>
-    <t>ZFJFROHCPHULKY-PKNBQFBNSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>KWOLFJPFCHCOCG-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C(c1ccccc1)C(F)(F)F</t>
-  </si>
-  <si>
-    <t>KZJRKRQSDZGHEC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Chem. Commun., 2010, 46, 8624-8626.</t>
-  </si>
-  <si>
-    <t>C=C(OC(=O)OCC)C1=C(C)C(=O)CCC1(C)C</t>
-  </si>
-  <si>
-    <t>HHZPPLBLSSEAQT-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey, P. D. S. Jardine, Tetrahedron Lett. 1989, 30, 7297-7300.</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCC(=O)c1ccc(C)cc1</t>
-  </si>
-  <si>
-    <t>ZAVHZGXNVXPEQL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1Oc1ccccc1</t>
-  </si>
-  <si>
-    <t>KPBCVVSDGJBODL-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COC(CC1=CCCC1=O)OC</t>
-  </si>
-  <si>
-    <t>JDVISUFZLXDPQJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>E. J. Corey et al., Tetrahedron Lett. 1988, 29, 3201-3204.</t>
-  </si>
-  <si>
-    <t>C=C(CC)C(C)=O</t>
-  </si>
-  <si>
-    <t>UOTSYAILGSUTAC-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>Takayama, Hiromitsu, et al. 1999, 1772-1773.</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>DJNJZIFFCJTUDS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1CCCC/C1=C\c1ccccc1</t>
-  </si>
-  <si>
-    <t>VCDPHYIZVFJQCD-ZRDIBKRKSA-N</t>
-  </si>
-  <si>
-    <t>O=C(CCc1ccccc1)C1CCCCC1</t>
-  </si>
-  <si>
-    <t>LFBKBXCVHMMYSM-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCC(=O)Cc1ccccc1</t>
-  </si>
-  <si>
-    <t>DYQAZJQDLPPHNB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)c1cccc(Br)c1</t>
-  </si>
-  <si>
-    <t>JYAQYXOVOHJRCS-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>COc1ccc(C(C)=O)cc1</t>
-  </si>
-  <si>
-    <t>NTPLXRHDUXRPNE-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O=C1C=CCC1</t>
-  </si>
-  <si>
-    <t>BZKFMUIJRXWWQK-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>O. Hamed, et al., Tetrahedron Lett. 2010, 51, 3514-3517.</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccccc1C</t>
-  </si>
-  <si>
-    <t>YXWWHNCQZBVZPV-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>J. H. Hutchinson, et al., "Polycyclic antagonists of lysophosphatidic acid receptors.", U.S. Patent No. 8,058,300. 15 Nov. 2011.</t>
-  </si>
-  <si>
-    <t>CC(=O)c1ccc(F)cc1</t>
-  </si>
-  <si>
-    <t>ZDPAWHACYDRYIW-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(C)(C)OC(=O)CN1CCC2(CC1)C(=O)Cc1ccccc12</t>
-  </si>
-  <si>
-    <t>IFROQBZVEYKUHT-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>T. Takemoto, et al., Tetrahedron Asymmetry. 1998, 10, 1787-1793.</t>
-  </si>
-  <si>
-    <t>CN(C)CCC(=O)c1ccc(Cl)c(Cl)c1</t>
-  </si>
-  <si>
-    <t>LZXMNZWXKWSYMY-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CC(=O)CCCC#N</t>
-  </si>
-  <si>
-    <t>AEVMBQIIZGKQRB-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>LXUIUVLDNRQBQJ-UHFFFAOYSA-N</t>
-  </si>
-  <si>
-    <t>CCCCCCCCCC(=O)c1ccccc1</t>
-  </si>
-  <si>
-    <t>QQXJNLYVPPBERR-UHFFFAOYSA-N</t>
   </si>
 </sst>
 </file>
@@ -4362,6 +4398,196 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1219200" y="119272050"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 96" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="120538875"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 97" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="121805700"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 98" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="123072525"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 99" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="124339350"/>
+          <a:ext cx="952500" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 100" descr="f"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="125606175"/>
           <a:ext cx="952500" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4659,7 +4885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
@@ -4696,7 +4922,7 @@
     </row>
     <row r="2" spans="1:9" ht="100" customHeight="1">
       <c r="A2">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -4705,13 +4931,13 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="F2">
-        <v>6.5</v>
+        <v>1.75</v>
       </c>
       <c r="G2">
-        <v>1.342331202326619</v>
+        <v>2.204267981024933</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -4722,7 +4948,7 @@
     </row>
     <row r="3" spans="1:9" ht="100" customHeight="1">
       <c r="A3">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -4731,16 +4957,16 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="F3">
-        <v>94</v>
+        <v>1.649999999999999</v>
       </c>
       <c r="G3">
-        <v>-1.330559931327695</v>
+        <v>2.139409515555571</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4748,25 +4974,25 @@
     </row>
     <row r="4" spans="1:9" ht="100" customHeight="1">
       <c r="A4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
       <c r="E4">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F4">
-        <v>4.5</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G4">
-        <v>1.79954597502246</v>
+        <v>-2.262087069087681</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4774,25 +5000,25 @@
     </row>
     <row r="5" spans="1:9" ht="100" customHeight="1">
       <c r="A5">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="F5">
-        <v>22.05</v>
+        <v>1.350000000000001</v>
       </c>
       <c r="G5">
-        <v>0.7614033784975828</v>
+        <v>2.24602855897637</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4800,25 +5026,25 @@
     </row>
     <row r="6" spans="1:9" ht="100" customHeight="1">
       <c r="A6">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>2.313504990947262</v>
+        <v>1.328058043046766</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4826,25 +5052,25 @@
     </row>
     <row r="7" spans="1:9" ht="100" customHeight="1">
       <c r="A7">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>1.536811490741356</v>
+        <v>1.278251167901181</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4852,25 +5078,25 @@
     </row>
     <row r="8" spans="1:9" ht="100" customHeight="1">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="G8">
-        <v>1.278251167901181</v>
+        <v>1.79954597502246</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4878,25 +5104,25 @@
     </row>
     <row r="9" spans="1:9" ht="100" customHeight="1">
       <c r="A9">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F9">
-        <v>69.75</v>
+        <v>1.200000000000003</v>
       </c>
       <c r="G9">
-        <v>-0.5037339428063619</v>
+        <v>2.598123523290279</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4904,25 +5130,25 @@
     </row>
     <row r="10" spans="1:9" ht="100" customHeight="1">
       <c r="A10">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>273</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>1.256928447975961</v>
+        <v>1.888460135226809</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4930,25 +5156,25 @@
     </row>
     <row r="11" spans="1:9" ht="100" customHeight="1">
       <c r="A11">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E11">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1.649999999999999</v>
       </c>
       <c r="G11">
-        <v>2.292437828399084</v>
+        <v>2.22075588496833</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4956,25 +5182,25 @@
     </row>
     <row r="12" spans="1:9" ht="100" customHeight="1">
       <c r="A12">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>295.5</v>
+        <v>273</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G12">
-        <v>2.044102454064183</v>
+        <v>1.990303135492853</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4982,25 +5208,25 @@
     </row>
     <row r="13" spans="1:9" ht="100" customHeight="1">
       <c r="A13">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="F13">
-        <v>3.350000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
-        <v>2.027267059394076</v>
+        <v>1.867911015042084</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -5008,25 +5234,25 @@
     </row>
     <row r="14" spans="1:9" ht="100" customHeight="1">
       <c r="A14">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E14">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14">
-        <v>1.7343923362882</v>
+        <v>1.804705539110695</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -5034,25 +5260,25 @@
     </row>
     <row r="15" spans="1:9" ht="100" customHeight="1">
       <c r="A15">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="F15">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>2.464891741858761</v>
+        <v>1.888460135226809</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -5060,25 +5286,25 @@
     </row>
     <row r="16" spans="1:9" ht="100" customHeight="1">
       <c r="A16">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E16">
-        <v>243</v>
+        <v>308</v>
       </c>
       <c r="F16">
-        <v>97.5</v>
+        <v>3.5</v>
       </c>
       <c r="G16">
-        <v>-1.771588505218915</v>
+        <v>2.0329208220246</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5086,25 +5312,25 @@
     </row>
     <row r="17" spans="1:9" ht="100" customHeight="1">
       <c r="A17">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E17">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>1.888460135226809</v>
+        <v>2.292437828399084</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5112,25 +5338,25 @@
     </row>
     <row r="18" spans="1:9" ht="100" customHeight="1">
       <c r="A18">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <v>296</v>
       </c>
       <c r="F18">
-        <v>1.200000000000003</v>
+        <v>1.5</v>
       </c>
       <c r="G18">
-        <v>2.598123523290279</v>
+        <v>2.464891741858761</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5138,25 +5364,25 @@
     </row>
     <row r="19" spans="1:9" ht="100" customHeight="1">
       <c r="A19">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="F19">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>-1.680937043443645</v>
+        <v>2.292437828399084</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -5164,25 +5390,25 @@
     </row>
     <row r="20" spans="1:9" ht="100" customHeight="1">
       <c r="A20">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E20">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20">
-        <v>1.804705539110695</v>
+        <v>1.7343923362882</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5190,25 +5416,25 @@
     </row>
     <row r="21" spans="1:9" ht="100" customHeight="1">
       <c r="A21">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E21">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F21">
-        <v>16.15</v>
+        <v>1.5</v>
       </c>
       <c r="G21">
-        <v>0.9931575781929751</v>
+        <v>2.464891741858761</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5216,25 +5442,25 @@
     </row>
     <row r="22" spans="1:9" ht="100" customHeight="1">
       <c r="A22">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>295.5</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>1.868838664666958</v>
+        <v>2.044102454064183</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5242,25 +5468,25 @@
     </row>
     <row r="23" spans="1:9" ht="100" customHeight="1">
       <c r="A23">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E23">
-        <v>303</v>
+        <v>295.5</v>
       </c>
       <c r="F23">
-        <v>37.1</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>0.3183254661622594</v>
+        <v>1.73146261950393</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5268,25 +5494,25 @@
     </row>
     <row r="24" spans="1:9" ht="100" customHeight="1">
       <c r="A24">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E24">
-        <v>303</v>
+        <v>295.5</v>
       </c>
       <c r="F24">
-        <v>24.65</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>0.6737387948132971</v>
+        <v>2.288565467202464</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5294,25 +5520,25 @@
     </row>
     <row r="25" spans="1:9" ht="100" customHeight="1">
       <c r="A25">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E25">
-        <v>273</v>
+        <v>295.5</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25">
-        <v>1.888460135226809</v>
+        <v>1.868838664666958</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5320,25 +5546,25 @@
     </row>
     <row r="26" spans="1:9" ht="100" customHeight="1">
       <c r="A26">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E26">
-        <v>296</v>
+        <v>295.5</v>
       </c>
       <c r="F26">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>2.157984352036207</v>
+        <v>1.73146261950393</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5346,25 +5572,25 @@
     </row>
     <row r="27" spans="1:9" ht="100" customHeight="1">
       <c r="A27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>295.5</v>
       </c>
       <c r="F27">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G27">
-        <v>0.9324201843062129</v>
+        <v>1.117849294725765</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5372,25 +5598,25 @@
     </row>
     <row r="28" spans="1:9" ht="100" customHeight="1">
       <c r="A28">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E28">
-        <v>303</v>
+        <v>295.5</v>
       </c>
       <c r="F28">
-        <v>47.4</v>
+        <v>17</v>
       </c>
       <c r="G28">
-        <v>0.06276549348197664</v>
+        <v>0.9324201843062129</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5398,25 +5624,25 @@
     </row>
     <row r="29" spans="1:9" ht="100" customHeight="1">
       <c r="A29">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E29">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="G29">
-        <v>1.7343923362882</v>
+        <v>2.106816252331982</v>
       </c>
       <c r="H29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5424,25 +5650,25 @@
     </row>
     <row r="30" spans="1:9" ht="100" customHeight="1">
       <c r="A30">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E30">
         <v>253</v>
       </c>
       <c r="F30">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G30">
-        <v>1.844493381976893</v>
+        <v>2.66502018010404</v>
       </c>
       <c r="H30" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5450,25 +5676,25 @@
     </row>
     <row r="31" spans="1:9" ht="100" customHeight="1">
       <c r="A31">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E31">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="G31">
-        <v>2.047561172260569</v>
+        <v>2.777872009783088</v>
       </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5476,25 +5702,25 @@
     </row>
     <row r="32" spans="1:9" ht="100" customHeight="1">
       <c r="A32">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E32">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F32">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>2.464891741858761</v>
+        <v>2.313504990947262</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5502,25 +5728,25 @@
     </row>
     <row r="33" spans="1:9" ht="100" customHeight="1">
       <c r="A33">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E33">
         <v>296</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>1.069278401948594</v>
+        <v>1.02174940566581</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5528,25 +5754,25 @@
     </row>
     <row r="34" spans="1:9" ht="100" customHeight="1">
       <c r="A34">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E34">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F34">
         <v>2.5</v>
       </c>
       <c r="G34">
-        <v>2.157984352036207</v>
+        <v>1.844493381976893</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5554,25 +5780,25 @@
     </row>
     <row r="35" spans="1:9" ht="100" customHeight="1">
       <c r="A35">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E35">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="F35">
-        <v>0.3999999999999986</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>2.777872009783088</v>
+        <v>1.979514389308825</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5580,25 +5806,25 @@
     </row>
     <row r="36" spans="1:9" ht="100" customHeight="1">
       <c r="A36">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E36">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F36">
-        <v>84</v>
+        <v>1.5</v>
       </c>
       <c r="G36">
-        <v>-0.8348680897275804</v>
+        <v>2.464891741858761</v>
       </c>
       <c r="H36" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5606,25 +5832,25 @@
     </row>
     <row r="37" spans="1:9" ht="100" customHeight="1">
       <c r="A37">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E37">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="F37">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>-2.036861989422158</v>
+        <v>2.047561172260569</v>
       </c>
       <c r="H37" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -5632,25 +5858,25 @@
     </row>
     <row r="38" spans="1:9" ht="100" customHeight="1">
       <c r="A38">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E38">
         <v>296</v>
       </c>
       <c r="F38">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G38">
-        <v>2.464891741858761</v>
+        <v>2.157984352036207</v>
       </c>
       <c r="H38" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -5658,25 +5884,25 @@
     </row>
     <row r="39" spans="1:9" ht="100" customHeight="1">
       <c r="A39">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E39">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G39">
-        <v>1.959414765489757</v>
+        <v>2.157984352036207</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -5684,25 +5910,25 @@
     </row>
     <row r="40" spans="1:9" ht="100" customHeight="1">
       <c r="A40">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E40">
         <v>243</v>
       </c>
       <c r="F40">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>-1.881967541557355</v>
+        <v>1.536811490741356</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -5710,25 +5936,25 @@
     </row>
     <row r="41" spans="1:9" ht="100" customHeight="1">
       <c r="A41">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E41">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="F41">
-        <v>6</v>
+        <v>85.5</v>
       </c>
       <c r="G41">
-        <v>1.38531548405723</v>
+        <v>-0.8580310015114321</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -5736,13 +5962,13 @@
     </row>
     <row r="42" spans="1:9" ht="100" customHeight="1">
       <c r="A42">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E42">
         <v>243</v>
@@ -5754,7 +5980,7 @@
         <v>-1.330559931327695</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -5762,25 +5988,25 @@
     </row>
     <row r="43" spans="1:9" ht="100" customHeight="1">
       <c r="A43">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E43">
-        <v>313</v>
+        <v>243</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="G43">
-        <v>1.979514389308825</v>
+        <v>-1.330559931327695</v>
       </c>
       <c r="H43" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -5788,25 +6014,25 @@
     </row>
     <row r="44" spans="1:9" ht="100" customHeight="1">
       <c r="A44">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E44">
-        <v>295.5</v>
+        <v>243</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="G44">
-        <v>1.73146261950393</v>
+        <v>-1.680937043443645</v>
       </c>
       <c r="H44" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -5814,25 +6040,25 @@
     </row>
     <row r="45" spans="1:9" ht="100" customHeight="1">
       <c r="A45">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E45">
-        <v>296</v>
+        <v>243</v>
       </c>
       <c r="F45">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="G45">
-        <v>1.523663491247452</v>
+        <v>-1.881967541557355</v>
       </c>
       <c r="H45" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -5840,25 +6066,25 @@
     </row>
     <row r="46" spans="1:9" ht="100" customHeight="1">
       <c r="A46">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E46">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="F46">
-        <v>1.350000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="G46">
-        <v>2.24602855897637</v>
+        <v>-1.771588505218915</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -5866,25 +6092,25 @@
     </row>
     <row r="47" spans="1:9" ht="100" customHeight="1">
       <c r="A47">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E47">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="G47">
-        <v>1.38531548405723</v>
+        <v>-2.77071941603565</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -5892,25 +6118,25 @@
     </row>
     <row r="48" spans="1:9" ht="100" customHeight="1">
       <c r="A48">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E48">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="F48">
-        <v>1.649999999999999</v>
+        <v>2</v>
       </c>
       <c r="G48">
-        <v>2.22075588496833</v>
+        <v>1.959414765489757</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5918,25 +6144,25 @@
     </row>
     <row r="49" spans="1:9" ht="100" customHeight="1">
       <c r="A49">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E49">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F49">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G49">
-        <v>1.02174940566581</v>
+        <v>1.750111407371365</v>
       </c>
       <c r="H49" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5944,25 +6170,25 @@
     </row>
     <row r="50" spans="1:9" ht="100" customHeight="1">
       <c r="A50">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E50">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="F50">
-        <v>90</v>
+        <v>4.5</v>
       </c>
       <c r="G50">
-        <v>-1.193686196129448</v>
+        <v>1.53812544486717</v>
       </c>
       <c r="H50" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5970,25 +6196,25 @@
     </row>
     <row r="51" spans="1:9" ht="100" customHeight="1">
       <c r="A51">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E51">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="F51">
-        <v>4.799999999999997</v>
+        <v>6.5</v>
       </c>
       <c r="G51">
-        <v>1.801290885481019</v>
+        <v>1.342331202326619</v>
       </c>
       <c r="H51" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5996,25 +6222,25 @@
     </row>
     <row r="52" spans="1:9" ht="100" customHeight="1">
       <c r="A52">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E52">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="F52">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>0.9955848522025851</v>
+        <v>1.38531548405723</v>
       </c>
       <c r="H52" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -6022,25 +6248,25 @@
     </row>
     <row r="53" spans="1:9" ht="100" customHeight="1">
       <c r="A53">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E53">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G53">
-        <v>1.523663491247452</v>
+        <v>1.750111407371365</v>
       </c>
       <c r="H53" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -6048,25 +6274,25 @@
     </row>
     <row r="54" spans="1:9" ht="100" customHeight="1">
       <c r="A54">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D54" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E54">
-        <v>296</v>
+        <v>253</v>
       </c>
       <c r="F54">
-        <v>41.5</v>
+        <v>6</v>
       </c>
       <c r="G54">
-        <v>0.2022370629367623</v>
+        <v>1.38531548405723</v>
       </c>
       <c r="H54" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -6074,25 +6300,25 @@
     </row>
     <row r="55" spans="1:9" ht="100" customHeight="1">
       <c r="A55">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E55">
-        <v>295.5</v>
+        <v>253</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G55">
-        <v>2.288565467202464</v>
+        <v>2.66502018010404</v>
       </c>
       <c r="H55" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -6100,25 +6326,25 @@
     </row>
     <row r="56" spans="1:9" ht="100" customHeight="1">
       <c r="A56">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E56">
         <v>296</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="G56">
-        <v>2.292437828399084</v>
+        <v>1.67514243026158</v>
       </c>
       <c r="H56" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -6126,25 +6352,25 @@
     </row>
     <row r="57" spans="1:9" ht="100" customHeight="1">
       <c r="A57">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E57">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F57">
-        <v>1.649999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="G57">
-        <v>2.139409515555571</v>
+        <v>1.669899246663064</v>
       </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -6152,25 +6378,25 @@
     </row>
     <row r="58" spans="1:9" ht="100" customHeight="1">
       <c r="A58">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E58">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="F58">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="G58">
-        <v>1.328058043046766</v>
+        <v>1.432821215513215</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -6178,25 +6404,25 @@
     </row>
     <row r="59" spans="1:9" ht="100" customHeight="1">
       <c r="A59">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59">
+        <v>295</v>
+      </c>
+      <c r="F59">
+        <v>15.5</v>
+      </c>
+      <c r="G59">
+        <v>0.9955848522025851</v>
+      </c>
+      <c r="H59" t="s">
         <v>146</v>
-      </c>
-      <c r="D59" t="s">
-        <v>147</v>
-      </c>
-      <c r="E59">
-        <v>253</v>
-      </c>
-      <c r="F59">
-        <v>0.5</v>
-      </c>
-      <c r="G59">
-        <v>2.66502018010404</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6204,25 +6430,25 @@
     </row>
     <row r="60" spans="1:9" ht="100" customHeight="1">
       <c r="A60">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B60" t="s">
+        <v>147</v>
+      </c>
+      <c r="D60" t="s">
         <v>148</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60">
+        <v>293</v>
+      </c>
+      <c r="F60">
+        <v>99</v>
+      </c>
+      <c r="G60">
+        <v>-2.679276531017972</v>
+      </c>
+      <c r="H60" t="s">
         <v>149</v>
-      </c>
-      <c r="E60">
-        <v>243</v>
-      </c>
-      <c r="F60">
-        <v>85.5</v>
-      </c>
-      <c r="G60">
-        <v>-0.8580310015114321</v>
-      </c>
-      <c r="H60" t="s">
-        <v>14</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6230,7 +6456,7 @@
     </row>
     <row r="61" spans="1:9" ht="100" customHeight="1">
       <c r="A61">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
         <v>150</v>
@@ -6239,16 +6465,16 @@
         <v>151</v>
       </c>
       <c r="E61">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F61">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>-2.77071941603565</v>
+        <v>2.026808863082253</v>
       </c>
       <c r="H61" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6256,7 +6482,7 @@
     </row>
     <row r="62" spans="1:9" ht="100" customHeight="1">
       <c r="A62">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B62" t="s">
         <v>152</v>
@@ -6265,16 +6491,16 @@
         <v>153</v>
       </c>
       <c r="E62">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G62">
-        <v>1.872000828228154</v>
+        <v>1.256928447975961</v>
       </c>
       <c r="H62" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6282,25 +6508,25 @@
     </row>
     <row r="63" spans="1:9" ht="100" customHeight="1">
       <c r="A63">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E63">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="F63">
-        <v>2.5</v>
+        <v>98</v>
       </c>
       <c r="G63">
-        <v>2.157984352036207</v>
+        <v>-2.036861989422158</v>
       </c>
       <c r="H63" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6308,25 +6534,25 @@
     </row>
     <row r="64" spans="1:9" ht="100" customHeight="1">
       <c r="A64">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E64">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F64">
-        <v>99</v>
+        <v>8.5</v>
       </c>
       <c r="G64">
-        <v>-2.679276531017972</v>
+        <v>1.409177301065802</v>
       </c>
       <c r="H64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6334,25 +6560,25 @@
     </row>
     <row r="65" spans="1:9" ht="100" customHeight="1">
       <c r="A65">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D65" t="s">
+        <v>162</v>
+      </c>
+      <c r="E65">
+        <v>298</v>
+      </c>
+      <c r="F65">
+        <v>4</v>
+      </c>
+      <c r="G65">
+        <v>1.884649482472939</v>
+      </c>
+      <c r="H65" t="s">
         <v>160</v>
-      </c>
-      <c r="E65">
-        <v>296</v>
-      </c>
-      <c r="F65">
-        <v>0.5</v>
-      </c>
-      <c r="G65">
-        <v>3.117968273955715</v>
-      </c>
-      <c r="H65" t="s">
-        <v>44</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6360,25 +6586,25 @@
     </row>
     <row r="66" spans="1:9" ht="100" customHeight="1">
       <c r="A66">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D66" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E66">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="F66">
-        <v>96</v>
+        <v>24.65</v>
       </c>
       <c r="G66">
-        <v>-1.726541304413128</v>
+        <v>0.6737387948132971</v>
       </c>
       <c r="H66" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6386,25 +6612,25 @@
     </row>
     <row r="67" spans="1:9" ht="100" customHeight="1">
       <c r="A67">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D67" t="s">
+        <v>167</v>
+      </c>
+      <c r="E67">
+        <v>303</v>
+      </c>
+      <c r="F67">
+        <v>16.15</v>
+      </c>
+      <c r="G67">
+        <v>0.9931575781929751</v>
+      </c>
+      <c r="H67" t="s">
         <v>165</v>
-      </c>
-      <c r="E67">
-        <v>293</v>
-      </c>
-      <c r="F67">
-        <v>3</v>
-      </c>
-      <c r="G67">
-        <v>2.026808863082253</v>
-      </c>
-      <c r="H67" t="s">
-        <v>166</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6412,25 +6638,25 @@
     </row>
     <row r="68" spans="1:9" ht="100" customHeight="1">
       <c r="A68">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E68">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="F68">
-        <v>2.5</v>
+        <v>68</v>
       </c>
       <c r="G68">
-        <v>1.990303135492853</v>
+        <v>-0.4545017836788858</v>
       </c>
       <c r="H68" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6438,25 +6664,25 @@
     </row>
     <row r="69" spans="1:9" ht="100" customHeight="1">
       <c r="A69">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E69">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>69.75</v>
       </c>
       <c r="G69">
-        <v>1.750111407371365</v>
+        <v>-0.5037339428063619</v>
       </c>
       <c r="H69" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6464,25 +6690,25 @@
     </row>
     <row r="70" spans="1:9" ht="100" customHeight="1">
       <c r="A70">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E70">
         <v>303</v>
       </c>
       <c r="F70">
-        <v>79.65000000000001</v>
+        <v>22.05</v>
       </c>
       <c r="G70">
-        <v>-0.8227894212201405</v>
+        <v>0.7614033784975828</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6490,25 +6716,25 @@
     </row>
     <row r="71" spans="1:9" ht="100" customHeight="1">
       <c r="A71">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E71">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F71">
-        <v>12</v>
+        <v>4.799999999999997</v>
       </c>
       <c r="G71">
-        <v>1.173621064209119</v>
+        <v>1.801290885481019</v>
       </c>
       <c r="H71" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -6516,25 +6742,25 @@
     </row>
     <row r="72" spans="1:9" ht="100" customHeight="1">
       <c r="A72">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E72">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F72">
-        <v>97.65000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="G72">
-        <v>-2.262087069087681</v>
+        <v>0.06276549348197664</v>
       </c>
       <c r="H72" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -6542,25 +6768,25 @@
     </row>
     <row r="73" spans="1:9" ht="100" customHeight="1">
       <c r="A73">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E73">
         <v>303</v>
       </c>
       <c r="F73">
-        <v>2.200000000000003</v>
+        <v>37.1</v>
       </c>
       <c r="G73">
-        <v>2.287949897639429</v>
+        <v>0.3183254661622594</v>
       </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -6568,25 +6794,25 @@
     </row>
     <row r="74" spans="1:9" ht="100" customHeight="1">
       <c r="A74">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E74">
         <v>303</v>
       </c>
       <c r="F74">
-        <v>8.5</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="G74">
-        <v>1.432821215513215</v>
+        <v>2.287949897639429</v>
       </c>
       <c r="H74" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -6594,7 +6820,7 @@
     </row>
     <row r="75" spans="1:9" ht="100" customHeight="1">
       <c r="A75">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B75" t="s">
         <v>182</v>
@@ -6603,16 +6829,16 @@
         <v>183</v>
       </c>
       <c r="E75">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="F75">
-        <v>3</v>
+        <v>45.35</v>
       </c>
       <c r="G75">
-        <v>1.750111407371365</v>
+        <v>0.1124774437798834</v>
       </c>
       <c r="H75" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -6620,7 +6846,7 @@
     </row>
     <row r="76" spans="1:9" ht="100" customHeight="1">
       <c r="A76">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
         <v>184</v>
@@ -6629,24 +6855,24 @@
         <v>185</v>
       </c>
       <c r="E76">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="F76">
-        <v>1.75</v>
+        <v>3.350000000000001</v>
       </c>
       <c r="G76">
-        <v>2.204267981024933</v>
+        <v>2.027267059394076</v>
       </c>
       <c r="H76" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="100" customHeight="1">
       <c r="A77">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
         <v>186</v>
@@ -6658,73 +6884,73 @@
         <v>303</v>
       </c>
       <c r="F77">
-        <v>92.45</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="G77">
-        <v>-1.5105124443152</v>
+        <v>-0.8227894212201405</v>
       </c>
       <c r="H77" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="100" customHeight="1">
       <c r="A78">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
+        <v>188</v>
+      </c>
+      <c r="D78" t="s">
         <v>189</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78">
+        <v>296</v>
+      </c>
+      <c r="F78">
+        <v>14.5</v>
+      </c>
+      <c r="G78">
+        <v>1.045173565627094</v>
+      </c>
+      <c r="H78" t="s">
         <v>190</v>
       </c>
-      <c r="E78">
-        <v>308</v>
-      </c>
-      <c r="F78">
-        <v>3.5</v>
-      </c>
-      <c r="G78">
-        <v>2.0329208220246</v>
-      </c>
-      <c r="H78" t="s">
-        <v>191</v>
-      </c>
       <c r="I78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="100" customHeight="1">
       <c r="A79">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
+        <v>191</v>
+      </c>
+      <c r="D79" t="s">
         <v>192</v>
-      </c>
-      <c r="D79" t="s">
-        <v>193</v>
       </c>
       <c r="E79">
         <v>296</v>
       </c>
       <c r="F79">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="G79">
-        <v>3.117968273955715</v>
+        <v>2.464891741858761</v>
       </c>
       <c r="H79" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="100" customHeight="1">
       <c r="A80">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="B80" t="s">
         <v>194</v>
@@ -6742,15 +6968,15 @@
         <v>2.157984352036207</v>
       </c>
       <c r="H80" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="I80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="100" customHeight="1">
       <c r="A81">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
         <v>196</v>
@@ -6759,42 +6985,42 @@
         <v>197</v>
       </c>
       <c r="E81">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="F81">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G81">
-        <v>1.867911015042084</v>
+        <v>1.872000828228154</v>
       </c>
       <c r="H81" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="100" customHeight="1">
       <c r="A82">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B82" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" t="s">
         <v>199</v>
       </c>
-      <c r="D82" t="s">
-        <v>200</v>
-      </c>
       <c r="E82">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F82">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="G82">
-        <v>1.669899246663064</v>
+        <v>1.523663491247452</v>
       </c>
       <c r="H82" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -6802,25 +7028,25 @@
     </row>
     <row r="83" spans="1:9" ht="100" customHeight="1">
       <c r="A83">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D83" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E83">
         <v>296</v>
       </c>
       <c r="F83">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G83">
-        <v>1.872000828228154</v>
+        <v>1.79954597502246</v>
       </c>
       <c r="H83" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="I83">
         <v>1</v>
@@ -6828,25 +7054,25 @@
     </row>
     <row r="84" spans="1:9" ht="100" customHeight="1">
       <c r="A84">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D84" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E84">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F84">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="G84">
-        <v>1.53812544486717</v>
+        <v>1.069278401948594</v>
       </c>
       <c r="H84" t="s">
-        <v>11</v>
+        <v>193</v>
       </c>
       <c r="I84">
         <v>1</v>
@@ -6854,25 +7080,25 @@
     </row>
     <row r="85" spans="1:9" ht="100" customHeight="1">
       <c r="A85">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D85" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E85">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F85">
-        <v>45.35</v>
+        <v>5</v>
       </c>
       <c r="G85">
-        <v>0.1124774437798834</v>
+        <v>1.7343923362882</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -6880,25 +7106,25 @@
     </row>
     <row r="86" spans="1:9" ht="100" customHeight="1">
       <c r="A86">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D86" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E86">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F86">
-        <v>68</v>
+        <v>0.5</v>
       </c>
       <c r="G86">
-        <v>-0.4545017836788858</v>
+        <v>3.117968273955715</v>
       </c>
       <c r="H86" t="s">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="I86">
         <v>1</v>
@@ -6906,13 +7132,13 @@
     </row>
     <row r="87" spans="1:9" ht="100" customHeight="1">
       <c r="A87">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D87" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E87">
         <v>296</v>
@@ -6924,7 +7150,7 @@
         <v>2.292437828399084</v>
       </c>
       <c r="H87" t="s">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="I87">
         <v>1</v>
@@ -6932,25 +7158,25 @@
     </row>
     <row r="88" spans="1:9" ht="100" customHeight="1">
       <c r="A88">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E88">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F88">
         <v>0.5</v>
       </c>
       <c r="G88">
-        <v>2.66502018010404</v>
+        <v>3.117968273955715</v>
       </c>
       <c r="H88" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="I88">
         <v>1</v>
@@ -6958,25 +7184,25 @@
     </row>
     <row r="89" spans="1:9" ht="100" customHeight="1">
       <c r="A89">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D89" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E89">
         <v>296</v>
       </c>
       <c r="F89">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="G89">
-        <v>1.045173565627094</v>
+        <v>1.523663491247452</v>
       </c>
       <c r="H89" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="I89">
         <v>1</v>
@@ -6984,25 +7210,25 @@
     </row>
     <row r="90" spans="1:9" ht="100" customHeight="1">
       <c r="A90">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B90" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D90" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E90">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="F90">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G90">
-        <v>1.801907092249077</v>
+        <v>2.157984352036207</v>
       </c>
       <c r="H90" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="I90">
         <v>1</v>
@@ -7010,25 +7236,25 @@
     </row>
     <row r="91" spans="1:9" ht="100" customHeight="1">
       <c r="A91">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E91">
-        <v>253</v>
+        <v>296</v>
       </c>
       <c r="F91">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="G91">
-        <v>2.106816252331982</v>
+        <v>1.872000828228154</v>
       </c>
       <c r="H91" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="I91">
         <v>1</v>
@@ -7036,25 +7262,25 @@
     </row>
     <row r="92" spans="1:9" ht="100" customHeight="1">
       <c r="A92">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D92" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E92">
         <v>296</v>
       </c>
       <c r="F92">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="G92">
-        <v>1.67514243026158</v>
+        <v>1.173621064209119</v>
       </c>
       <c r="H92" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -7062,25 +7288,25 @@
     </row>
     <row r="93" spans="1:9" ht="100" customHeight="1">
       <c r="A93">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D93" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E93">
-        <v>295.5</v>
+        <v>296</v>
       </c>
       <c r="F93">
-        <v>5</v>
+        <v>41.5</v>
       </c>
       <c r="G93">
-        <v>1.73146261950393</v>
+        <v>0.2022370629367623</v>
       </c>
       <c r="H93" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -7088,25 +7314,25 @@
     </row>
     <row r="94" spans="1:9" ht="100" customHeight="1">
       <c r="A94">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D94" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E94">
-        <v>295.5</v>
+        <v>303</v>
       </c>
       <c r="F94">
-        <v>13</v>
+        <v>92.45</v>
       </c>
       <c r="G94">
-        <v>1.117849294725765</v>
+        <v>-1.5105124443152</v>
       </c>
       <c r="H94" t="s">
-        <v>63</v>
+        <v>224</v>
       </c>
       <c r="I94">
         <v>1</v>
@@ -7114,25 +7340,25 @@
     </row>
     <row r="95" spans="1:9" ht="100" customHeight="1">
       <c r="A95">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D95" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E95">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F95">
-        <v>4.5</v>
+        <v>94</v>
       </c>
       <c r="G95">
-        <v>1.79954597502246</v>
+        <v>-1.631715471340137</v>
       </c>
       <c r="H95" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="I95">
         <v>1</v>
@@ -7140,27 +7366,157 @@
     </row>
     <row r="96" spans="1:9" ht="100" customHeight="1">
       <c r="A96">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B96" t="s">
+        <v>228</v>
+      </c>
+      <c r="D96" t="s">
+        <v>229</v>
+      </c>
+      <c r="E96">
+        <v>273</v>
+      </c>
+      <c r="F96">
+        <v>3.5</v>
+      </c>
+      <c r="G96">
+        <v>1.801907092249077</v>
+      </c>
+      <c r="H96" t="s">
+        <v>230</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="100" customHeight="1">
+      <c r="A97">
+        <v>102</v>
+      </c>
+      <c r="B97" t="s">
         <v>231</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D97" t="s">
         <v>232</v>
       </c>
-      <c r="E96">
-        <v>296</v>
-      </c>
-      <c r="F96">
-        <v>1.5</v>
-      </c>
-      <c r="G96">
-        <v>2.464891741858761</v>
-      </c>
-      <c r="H96" t="s">
-        <v>44</v>
-      </c>
-      <c r="I96">
+      <c r="E97">
+        <v>243</v>
+      </c>
+      <c r="F97">
+        <v>99.5</v>
+      </c>
+      <c r="G97">
+        <v>-2.559683414092031</v>
+      </c>
+      <c r="H97" t="s">
+        <v>233</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="100" customHeight="1">
+      <c r="A98">
+        <v>103</v>
+      </c>
+      <c r="B98" t="s">
+        <v>234</v>
+      </c>
+      <c r="D98" t="s">
+        <v>235</v>
+      </c>
+      <c r="E98">
+        <v>243</v>
+      </c>
+      <c r="F98">
+        <v>99.5</v>
+      </c>
+      <c r="G98">
+        <v>-2.559683414092031</v>
+      </c>
+      <c r="H98" t="s">
+        <v>233</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="100" customHeight="1">
+      <c r="A99">
+        <v>104</v>
+      </c>
+      <c r="B99" t="s">
+        <v>236</v>
+      </c>
+      <c r="D99" t="s">
+        <v>237</v>
+      </c>
+      <c r="E99">
+        <v>253</v>
+      </c>
+      <c r="F99">
+        <v>84</v>
+      </c>
+      <c r="G99">
+        <v>-0.8348680897275804</v>
+      </c>
+      <c r="H99" t="s">
+        <v>238</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="100" customHeight="1">
+      <c r="A100">
+        <v>105</v>
+      </c>
+      <c r="B100" t="s">
+        <v>239</v>
+      </c>
+      <c r="D100" t="s">
+        <v>240</v>
+      </c>
+      <c r="E100">
+        <v>273</v>
+      </c>
+      <c r="F100">
+        <v>96</v>
+      </c>
+      <c r="G100">
+        <v>-1.726541304413128</v>
+      </c>
+      <c r="H100" t="s">
+        <v>241</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="100" customHeight="1">
+      <c r="A101">
+        <v>106</v>
+      </c>
+      <c r="B101" t="s">
+        <v>242</v>
+      </c>
+      <c r="D101" t="s">
+        <v>243</v>
+      </c>
+      <c r="E101">
+        <v>273</v>
+      </c>
+      <c r="F101">
+        <v>90</v>
+      </c>
+      <c r="G101">
+        <v>-1.193686196129448</v>
+      </c>
+      <c r="H101" t="s">
+        <v>244</v>
+      </c>
+      <c r="I101">
         <v>1</v>
       </c>
     </row>
